--- a/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
+++ b/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-30T19:11:20-07:00</t>
+    <t>2026-02-02T11:11:20-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
+++ b/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T11:11:20-06:00</t>
+    <t>2026-02-04T10:26:00-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
+++ b/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T00:24:16-05:00</t>
+    <t>2026-05-25T15:07:02-06:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
+++ b/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
+++ b/docs/StructureDefinition-space-nutrition-inventory-item.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="190">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/space-nutrition-inventory-item</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/space-nutrition-inventory-item</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -447,7 +450,7 @@
     <t>inventoryRiskFlag</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/inventory-risk-flag}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/inventory-risk-flag}
 </t>
   </si>
   <si>
@@ -873,54 +876,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -943,7 +948,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.71484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="83.4765625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -974,137 +979,137 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1116,13 +1121,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1173,22 +1178,22 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AL2" t="s" s="2">
         <v>20</v>
@@ -1196,10 +1201,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1207,10 +1212,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1219,19 +1224,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1281,13 +1286,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1304,10 +1309,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1315,10 +1320,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1327,16 +1332,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1387,19 +1392,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1410,10 +1415,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1421,31 +1426,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1495,19 +1500,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1518,10 +1523,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1529,10 +1534,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1544,16 +1549,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1579,13 +1584,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1603,19 +1608,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -1626,21 +1631,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1652,16 +1657,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1711,22 +1716,22 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>20</v>
@@ -1734,21 +1739,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1760,16 +1765,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1819,13 +1824,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1834,7 +1839,7 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>20</v>
@@ -1842,10 +1847,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1853,10 +1858,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -1868,13 +1873,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1913,29 +1918,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -1946,26 +1951,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -1974,13 +1979,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2031,19 +2036,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2054,45 +2059,45 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2141,22 +2146,22 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>20</v>
@@ -2164,10 +2169,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2175,10 +2180,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2187,16 +2192,16 @@
         <v>20</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2247,33 +2252,33 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2281,34 +2286,34 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2318,7 +2323,7 @@
         <v>20</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="T13" t="s" s="2">
         <v>20</v>
@@ -2333,13 +2338,13 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>20</v>
@@ -2357,33 +2362,33 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2391,34 +2396,34 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -2467,33 +2472,33 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2501,10 +2506,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2513,20 +2518,20 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -2575,33 +2580,33 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2609,10 +2614,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2621,20 +2626,20 @@
         <v>20</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -2683,25 +2688,25 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
